--- a/data/trans_dic/ProbViv_temp-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 44,71</t>
+          <t>29,03; 44,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,94; 47,44</t>
+          <t>33,0; 46,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,46; 43,24</t>
+          <t>32,54; 43,61</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 48,69</t>
+          <t>36,78; 48,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,91; 65,87</t>
+          <t>33,56; 66,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,58; 56,68</t>
+          <t>37,63; 57,69</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,38; 40,59</t>
+          <t>32,61; 41,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,24; 36,93</t>
+          <t>24,37; 36,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 37,41</t>
+          <t>29,85; 37,51</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 38,4</t>
+          <t>11,24; 38,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,5; 44,31</t>
+          <t>32,86; 43,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 39,81</t>
+          <t>20,72; 40,15</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,88; 43,65</t>
+          <t>36,16; 43,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,1; 47,35</t>
+          <t>41,23; 47,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,22; 44,59</t>
+          <t>39,57; 44,68</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,39; 46,47</t>
+          <t>38,37; 46,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 40,19</t>
+          <t>11,61; 40,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,54; 41,85</t>
+          <t>17,86; 42,01</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,0; 48,33</t>
+          <t>38,66; 48,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,04; 43,94</t>
+          <t>37,11; 43,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,95; 44,15</t>
+          <t>39,13; 44,57</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,03; 39,9</t>
+          <t>28,49; 40,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,37; 41,33</t>
+          <t>30,99; 41,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,85</t>
+          <t>32,72; 40,09</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>114167; 178832</t>
+          <t>116103; 176926</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103153; 148579</t>
+          <t>103352; 145575</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>231486; 308364</t>
+          <t>232057; 311030</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>156062; 206232</t>
+          <t>155763; 207164</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173642; 337332</t>
+          <t>171854; 341938</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>351649; 530354</t>
+          <t>352127; 539801</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>173642; 217691</t>
+          <t>174910; 220239</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>143506; 218646</t>
+          <t>144283; 217921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>334186; 422107</t>
+          <t>336812; 423192</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116650; 340936</t>
+          <t>99778; 341347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>245929; 315897</t>
+          <t>234242; 313332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>299778; 637250</t>
+          <t>331646; 642612</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>201384; 244987</t>
+          <t>202970; 246519</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>225179; 259409</t>
+          <t>225885; 259643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>435010; 494548</t>
+          <t>438878; 495608</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>141323; 171077</t>
+          <t>141258; 172344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66707; 244491</t>
+          <t>70655; 245596</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>181094; 408640</t>
+          <t>174412; 410282</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>110272; 136665</t>
+          <t>109308; 136159</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>157748; 187097</t>
+          <t>158036; 186264</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275999; 312846</t>
+          <t>277279; 315847</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>969935; 1380426</t>
+          <t>985624; 1385169</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1127339; 1534209</t>
+          <t>1150352; 1537056</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2314614; 2858358</t>
+          <t>2346364; 2875222</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 44,23</t>
+          <t>32,37; 47,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,0; 46,48</t>
+          <t>36,61; 51,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 43,61</t>
+          <t>36,75; 47,28</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,78; 48,91</t>
+          <t>37,59; 49,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,56; 66,77</t>
+          <t>33,1; 42,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,63; 57,69</t>
+          <t>36,85; 44,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,61; 41,06</t>
+          <t>34,68; 42,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,37; 36,81</t>
+          <t>32,7; 39,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,85; 37,51</t>
+          <t>34,4; 39,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 38,45</t>
+          <t>35,02; 42,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,86; 43,95</t>
+          <t>41,02; 46,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 40,15</t>
+          <t>39,14; 43,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,16; 43,92</t>
+          <t>37,09; 44,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,23; 47,39</t>
+          <t>42,06; 48,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,57; 44,68</t>
+          <t>40,15; 45,26</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,37; 46,81</t>
+          <t>38,66; 46,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,61; 40,37</t>
+          <t>36,54; 43,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,86; 42,01</t>
+          <t>39,05; 44,44</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 48,15</t>
+          <t>39,5; 48,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,11; 43,74</t>
+          <t>37,54; 44,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,13; 44,57</t>
+          <t>39,53; 45,43</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,49; 40,04</t>
+          <t>38,93; 42,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,4</t>
+          <t>39,78; 42,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,72; 40,09</t>
+          <t>39,82; 42,08</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>145353</t>
+          <t>164369</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>124889</t>
+          <t>160784</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270242</t>
+          <t>325152</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>116103; 176926</t>
+          <t>131987; 194472</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103352; 145575</t>
+          <t>132731; 186858</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232057; 311030</t>
+          <t>283050; 364197</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>181070</t>
+          <t>207702</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>223834</t>
+          <t>188163</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404904</t>
+          <t>395865</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155763; 207164</t>
+          <t>179258; 235269</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>171854; 341938</t>
+          <t>166064; 211171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>352127; 539801</t>
+          <t>360661; 434154</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>196810</t>
+          <t>239262</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>192720</t>
+          <t>223817</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389530</t>
+          <t>463078</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>174910; 220239</t>
+          <t>215286; 265702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>144283; 217921</t>
+          <t>203806; 244916</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>336812; 423192</t>
+          <t>427926; 493478</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>238055</t>
+          <t>271905</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>289731</t>
+          <t>324356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527786</t>
+          <t>596262</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99778; 341347</t>
+          <t>245340; 299116</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>234242; 313332</t>
+          <t>302300; 345724</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>331646; 642612</t>
+          <t>562657; 631909</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>223830</t>
+          <t>247273</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>241797</t>
+          <t>275091</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465626</t>
+          <t>522364</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>202970; 246519</t>
+          <t>226000; 271167</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>225885; 259643</t>
+          <t>256090; 293591</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438878; 495608</t>
+          <t>489106; 551389</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>156581</t>
+          <t>173947</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>158752</t>
+          <t>176694</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315333</t>
+          <t>350641</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>141258; 172344</t>
+          <t>157358; 190588</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>70655; 245596</t>
+          <t>160463; 190660</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>174412; 410282</t>
+          <t>330442; 376095</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>122816</t>
+          <t>137051</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>171767</t>
+          <t>191592</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294582</t>
+          <t>328643</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>109308; 136159</t>
+          <t>122523; 151793</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>158036; 186264</t>
+          <t>174427; 207754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>277279; 315847</t>
+          <t>306314; 352032</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1264515</t>
+          <t>1441509</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1403489</t>
+          <t>1540497</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2668004</t>
+          <t>2982006</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>985624; 1385169</t>
+          <t>1375418; 1505660</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1150352; 1537056</t>
+          <t>1486416; 1595252</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2346364; 2875222</t>
+          <t>2894695; 3059329</t>
         </is>
       </c>
     </row>
